--- a/Documents/Product Catalog/10 Bed Room Set-3.xlsx
+++ b/Documents/Product Catalog/10 Bed Room Set-3.xlsx
@@ -4490,7 +4490,9 @@
         <f>L31*(1-0.1)</f>
         <v/>
       </c>
-      <c r="L31" s="14" t="n"/>
+      <c r="L31" s="14" t="n">
+        <v>30500</v>
+      </c>
       <c r="M31" s="15" t="n">
         <v>0.1</v>
       </c>
@@ -4629,7 +4631,9 @@
         <f>L32*(1-0.1)</f>
         <v/>
       </c>
-      <c r="L32" s="14" t="n"/>
+      <c r="L32" s="14" t="n">
+        <v>10000</v>
+      </c>
       <c r="M32" s="15" t="n">
         <v>0.1</v>
       </c>
@@ -5181,7 +5185,7 @@
         <v/>
       </c>
       <c r="L37" s="14" t="n">
-        <v>13500</v>
+        <v>10990</v>
       </c>
       <c r="M37" s="15" t="n">
         <v>0.1</v>
@@ -5282,7 +5286,7 @@
         <v/>
       </c>
       <c r="L38" s="14" t="n">
-        <v>10990</v>
+        <v>13500</v>
       </c>
       <c r="M38" s="15" t="n">
         <v>0.1</v>
@@ -5484,7 +5488,7 @@
         <v/>
       </c>
       <c r="L40" s="14" t="n">
-        <v>25500</v>
+        <v>22000</v>
       </c>
       <c r="M40" s="15" t="n">
         <v>0.1</v>
@@ -5588,7 +5592,7 @@
         <v/>
       </c>
       <c r="L41" s="14" t="n">
-        <v>25500</v>
+        <v>23200</v>
       </c>
       <c r="M41" s="15" t="n">
         <v>0.1</v>
@@ -5691,7 +5695,9 @@
         <f>L42*(1-0.1)</f>
         <v/>
       </c>
-      <c r="L42" s="14" t="n"/>
+      <c r="L42" s="14" t="n">
+        <v>23500</v>
+      </c>
       <c r="M42" s="15" t="n">
         <v>0.1</v>
       </c>
@@ -6431,7 +6437,7 @@
         <v/>
       </c>
       <c r="L49" s="14" t="n">
-        <v>23000</v>
+        <v>22500</v>
       </c>
       <c r="M49" s="15" t="n">
         <v>0.1</v>
@@ -6536,7 +6542,7 @@
         <v/>
       </c>
       <c r="L50" s="14" t="n">
-        <v>44500</v>
+        <v>42990</v>
       </c>
       <c r="M50" s="15" t="n">
         <v>0.1</v>
@@ -6645,7 +6651,7 @@
         <v/>
       </c>
       <c r="L51" s="14" t="n">
-        <v>45500</v>
+        <v>43990</v>
       </c>
       <c r="M51" s="15" t="n">
         <v>0.1</v>
@@ -6753,7 +6759,9 @@
         <f>L52*(1-0.1)</f>
         <v/>
       </c>
-      <c r="L52" s="14" t="n"/>
+      <c r="L52" s="14" t="n">
+        <v>57500</v>
+      </c>
       <c r="M52" s="15" t="n">
         <v>0.1</v>
       </c>
@@ -7081,7 +7089,7 @@
         <v/>
       </c>
       <c r="L55" s="14" t="n">
-        <v>33000</v>
+        <v>32500</v>
       </c>
       <c r="M55" s="15" t="n">
         <v>0.1</v>
